--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,14 +553,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 10/10  ·  전일분: RISE, TIGER 기술이전, TIGER 코스닥, MIDAS  ·  전부 반영 완료</t>
+          <t>캡처 10/10  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,313억   ·   현금 -7억(-0.1%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 1종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,566억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -649,14 +649,14 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>코나아이 ※</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
         <v>38</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>856562214</v>
+        <v>857423934</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,932억   ·   현금 74억(2.5%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,983억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -773,7 +773,7 @@
         <v>36</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1453766021</v>
+        <v>1453766346</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>-24</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>-2944907232</v>
+        <v>-2944907890</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>5952643448</v>
+        <v>5952644778</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>-8</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>-5894110463</v>
+        <v>-5894111780</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,112억   ·   현금 45억(2.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,229억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -950,7 +950,7 @@
         <v>53</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2238353490</v>
+        <v>2251859375</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>-244</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>-3979589759</v>
+        <v>-4003602000</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>51</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2109930436</v>
+        <v>2122661436</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>-49</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>-909635671</v>
+        <v>-915124274</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2302399267</v>
+        <v>2316291595</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>-36</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>-1923760104</v>
+        <v>-1935367780</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-27</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>-934431862</v>
+        <v>-940070082</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,032억   ·   현금 7억(0.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,074억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1199,7 +1199,7 @@
         <v>86</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1490517305</v>
+        <v>1486828495</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>-63</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>-964630609</v>
+        <v>-962243291</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>52</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1081911786</v>
+        <v>1079234214</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>-62</v>
       </c>
       <c r="I26" s="16" t="n">
-        <v>-1933705217</v>
+        <v>-1928919583</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>-3</v>
       </c>
       <c r="I27" s="16" t="n">
-        <v>-52903790</v>
+        <v>-52772860</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억   ·   현금 2억(0.9%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 253억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1332,7 +1332,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 409억   ·   현금 -2억(-0.4%)      ※전일분  PDF 2026-10-28  vs  2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 -2억(-0.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1356,7 +1356,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억   ·   현금 69억(6.9%)      ※전일분  PDF 2026-10-28  vs  2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 70억(6.7%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1380,7 +1380,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억   ·   현금 2억(0.2%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 4종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 913억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1476,7 +1476,7 @@
         <v>255</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1109760261</v>
+        <v>1109759608</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>-67</v>
       </c>
       <c r="I41" s="16" t="n">
-        <v>-425416600</v>
+        <v>-425416350</v>
       </c>
       <c r="J41" s="17" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>94</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>284763667</v>
+        <v>284763499</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>-20</v>
       </c>
       <c r="I42" s="16" t="n">
-        <v>-935000220</v>
+        <v>-934999670</v>
       </c>
       <c r="J42" s="17" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>66</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>466752110</v>
+        <v>466751835</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>-8</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>-312120073</v>
+        <v>-312119890</v>
       </c>
       <c r="J43" s="17" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>91613022</v>
+        <v>91612968</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>-4</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>-284580067</v>
+        <v>-284579900</v>
       </c>
       <c r="J44" s="17" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억   ·   현금 3억(1.1%)      ※전일분  PDF 2026-10-28  vs  2026-10-27      매수 5종목  /  매도 7종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 0억(0.1%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -1734,132 +1734,132 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>와이씨  (신규)</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>267208890</v>
+        <v>319185284</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.05%→3.12%</t>
+          <t>0.00%→1.04%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>26→37</t>
+          <t>0→54</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="H49" s="16" t="n">
-        <v>-81</v>
+        <v>-72</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>-247232426</v>
+        <v>-110487214</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>2.97%→2.02%</t>
+          <t>0.94%→0.49%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>272→191</t>
+          <t>170→98</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아이씨티케이  (신규)</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>78832306</v>
+        <v>331663721</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>4.04%→4.81%</t>
+          <t>0.00%→1.08%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>83→88</t>
+          <t>0→39</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>HLB이노베이션  (편출)</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="H50" s="16" t="n">
-        <v>-29</v>
+        <v>-24</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>-181425869</v>
+        <v>-97705657</v>
       </c>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>0.66%→0.00%</t>
+          <t>0.88%→0.49%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>29→0</t>
+          <t>61→37</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>태웅  (신규)</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>187934534</v>
+        <v>300004529</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.44%→1.14%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>3→7</t>
+          <t>0→28</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>파인엠텍</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="H51" s="16" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>-66686448</v>
+        <v>-139338337</v>
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>1.10%→0.88%</t>
+          <t>1.30%→0.75%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>77→61</t>
+          <t>61→38</t>
         </is>
       </c>
     </row>
@@ -1870,84 +1870,68 @@
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>148023705</v>
+        <v>214709949</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.33%</t>
+          <t>6.33%→7.15%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>37→41</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H52" s="16" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>-138930099</v>
+        <v>-97714077</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>3.58%→2.80%</t>
+          <t>1.08%→0.69%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>75→64</t>
+          <t>35→24</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>43889281</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.94%→1.01%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>17→20</t>
-        </is>
-      </c>
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="14" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H53" s="16" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-98892970</v>
+        <v>-305645927</v>
       </c>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>1.99%→1.31%</t>
+          <t>2.76%→1.53%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>29→23</t>
+          <t>28→17</t>
         </is>
       </c>
     </row>
@@ -1959,23 +1943,23 @@
       <c r="E54" s="14" t="n"/>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H54" s="16" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>-113670081</v>
+        <v>-143603066</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>3.34%→2.76%</t>
+          <t>1.31%→0.73%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>32→28</t>
+          <t>23→14</t>
         </is>
       </c>
     </row>
@@ -1987,45 +1971,73 @@
       <c r="E55" s="14" t="n"/>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>태성</t>
         </is>
       </c>
       <c r="H55" s="16" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>-152570509</v>
+        <v>-159432662</v>
       </c>
       <c r="J55" s="17" t="inlineStr">
         <is>
-          <t>3.65%→2.78%</t>
+          <t>2.04%→1.48%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>25→21</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억   ·   현금 1억(1.7%)      ※전일분  PDF 2026-10-28  vs  2026-10-27      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+          <t>27→20</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="14" t="n"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="14" t="n"/>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>-87988979</v>
+      </c>
+      <c r="J56" s="17" t="inlineStr">
+        <is>
+          <t>1.01%→0.69%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>17→12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -2037,6 +2049,7 @@
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
@@ -2044,7 +2057,6 @@
     <mergeCell ref="A46:K46"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G15:K15"/>
-    <mergeCell ref="A57:K57"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A47:E47"/>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -1332,7 +1332,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 -2억(-0.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1356,7 +1356,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 70억(6.7%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 0억(0.1%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 8종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2022,7 +2022,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -1887,23 +1887,23 @@
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H52" s="16" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>-97714077</v>
+        <v>-305645927</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>1.08%→0.69%</t>
+          <t>2.76%→1.53%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>35→24</t>
+          <t>28→17</t>
         </is>
       </c>
     </row>
@@ -1915,23 +1915,23 @@
       <c r="E53" s="14" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H53" s="16" t="n">
         <v>-11</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-305645927</v>
+        <v>-97714077</v>
       </c>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>2.76%→1.53%</t>
+          <t>1.08%→0.69%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>28→17</t>
+          <t>35→24</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,13 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -162,6 +172,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -546,14 +560,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>코스닥 액티브 ETF PDF 변화   ·   당일 2026-10-29  vs  전영업일 2026-10-28</t>
+          <t>액티브 ETF PDF 변화   ·   당일 2026-10-29  vs  전영업일 2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 10/10  ·  전부 반영 완료</t>
+          <t>캡처 16/19  ·  대기: RISE 비메모리, RISE 반도체소, RISE 2차전지</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2036,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 34억(1.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2043,34 +2057,592 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="20" t="n"/>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="20" t="n"/>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>761484000</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>4.31%→5.14%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>-832396500</v>
+      </c>
+      <c r="J66" s="17" t="inlineStr">
+        <is>
+          <t>2.89%→1.78%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>890692000</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>3.07%→4.19%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>63→85</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>-807007500</v>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>1.96%→0.91%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>225→108</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="20" t="n"/>
+      <c r="F72" s="20" t="n"/>
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20" t="n"/>
+      <c r="I72" s="20" t="n"/>
+      <c r="J72" s="20" t="n"/>
+      <c r="K72" s="20" t="n"/>
+    </row>
+    <row r="74" ht="19" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억   ·   현금 -6억(-4.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>258</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>231168132</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→2.69%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>208→466</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>코세스  (편출)</t>
+        </is>
+      </c>
+      <c r="H77" s="16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I77" s="16" t="n">
+        <v>-139562580</v>
+      </c>
+      <c r="J77" s="17" t="inlineStr">
+        <is>
+          <t>0.98%→0.00%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>110→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>119392068</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>2.20%→2.95%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>232→314</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="n"/>
+      <c r="H78" s="14" t="n"/>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>71400041</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>0.92%→1.38%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>32→48</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="n"/>
+      <c r="H79" s="14" t="n"/>
+      <c r="I79" s="14" t="n"/>
+      <c r="J79" s="14" t="n"/>
+      <c r="K79" s="14" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>유니퀘스트</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>1576401</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>7.79%→6.82%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>2,677→2,681</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="n"/>
+      <c r="H80" s="14" t="n"/>
+      <c r="I80" s="14" t="n"/>
+      <c r="J80" s="14" t="n"/>
+      <c r="K80" s="14" t="n"/>
+    </row>
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="20" t="n"/>
+      <c r="F82" s="20" t="n"/>
+      <c r="G82" s="20" t="n"/>
+      <c r="H82" s="20" t="n"/>
+      <c r="I82" s="20" t="n"/>
+      <c r="J82" s="20" t="n"/>
+      <c r="K82" s="20" t="n"/>
+    </row>
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 1억(0.5%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="45">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A82:K82"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A87:K87"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A74:K74"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="G64:K64"/>
     <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A72:K72"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="G47:K47"/>
     <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="G75:K75"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="G9:K9"/>
   </mergeCells>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,13 +62,8 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -100,11 +95,6 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,10 +162,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 16/19  ·  대기: RISE 비메모리, RISE 반도체소, RISE 2차전지</t>
+          <t>캡처 19/19  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2022,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 34억(1.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2058,421 +2044,476 @@
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
-        <is>
-          <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-      <c r="H61" s="20" t="n"/>
-      <c r="I61" s="20" t="n"/>
-      <c r="J61" s="20" t="n"/>
-      <c r="K61" s="20" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 비메모리반도체액티브  (KB)      순자산 ≈ 2,226억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>이수페타시스</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>1144756800</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>5.50%→6.11%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>294→321</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>-2367390000</v>
+      </c>
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>6.83%→5.12%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>291→241</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>317988000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>19.83%→20.36%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>425→428</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="n"/>
+      <c r="H65" s="14" t="n"/>
+      <c r="I65" s="14" t="n"/>
+      <c r="J65" s="14" t="n"/>
+      <c r="K65" s="14" t="n"/>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
+      <c r="B70" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C66" s="11" t="n">
+      <c r="C70" s="11" t="n">
         <v>761484000</v>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>4.31%→5.14%</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>209→255</t>
         </is>
       </c>
-      <c r="G66" s="15" t="inlineStr">
+      <c r="G70" s="15" t="inlineStr">
         <is>
           <t>대한전선</t>
         </is>
       </c>
-      <c r="H66" s="16" t="n">
+      <c r="H70" s="16" t="n">
         <v>-1215</v>
       </c>
-      <c r="I66" s="16" t="n">
+      <c r="I70" s="16" t="n">
         <v>-832396500</v>
       </c>
-      <c r="J66" s="17" t="inlineStr">
+      <c r="J70" s="17" t="inlineStr">
         <is>
           <t>2.89%→1.78%</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K70" s="13" t="inlineStr">
         <is>
           <t>3,349→2,134</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B67" s="11" t="n">
+      <c r="B71" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C67" s="11" t="n">
+      <c r="C71" s="11" t="n">
         <v>890692000</v>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>3.07%→4.19%</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>63→85</t>
         </is>
       </c>
-      <c r="G67" s="15" t="inlineStr">
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>삼성에스디에스</t>
         </is>
       </c>
-      <c r="H67" s="16" t="n">
+      <c r="H71" s="16" t="n">
         <v>-117</v>
       </c>
-      <c r="I67" s="16" t="n">
+      <c r="I71" s="16" t="n">
         <v>-807007500</v>
       </c>
-      <c r="J67" s="17" t="inlineStr">
+      <c r="J71" s="17" t="inlineStr">
         <is>
           <t>1.96%→0.91%</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K71" s="13" t="inlineStr">
         <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+    <row r="73" ht="19" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="19" customHeight="1">
-      <c r="A72" s="19" t="inlineStr">
-        <is>
-          <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B72" s="20" t="n"/>
-      <c r="C72" s="20" t="n"/>
-      <c r="D72" s="20" t="n"/>
-      <c r="E72" s="20" t="n"/>
-      <c r="F72" s="20" t="n"/>
-      <c r="G72" s="20" t="n"/>
-      <c r="H72" s="20" t="n"/>
-      <c r="I72" s="20" t="n"/>
-      <c r="J72" s="20" t="n"/>
-      <c r="K72" s="20" t="n"/>
-    </row>
-    <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억   ·   현금 -6억(-4.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 1종목</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="76" ht="19" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 반도체소부장액티브  (KB)      순자산 ≈ 174억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 3종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="8" t="n"/>
-      <c r="J75" s="8" t="n"/>
-      <c r="K75" s="8" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J76" s="9" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>미코</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="n">
-        <v>258</v>
-      </c>
-      <c r="C77" s="11" t="n">
-        <v>231168132</v>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>1.12%→2.69%</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>208→466</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr">
-        <is>
-          <t>코세스  (편출)</t>
-        </is>
-      </c>
-      <c r="H77" s="16" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I77" s="16" t="n">
-        <v>-139562580</v>
-      </c>
-      <c r="J77" s="17" t="inlineStr">
-        <is>
-          <t>0.98%→0.00%</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>110→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="C78" s="11" t="n">
-        <v>119392068</v>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>2.20%→2.95%</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>232→314</t>
-        </is>
-      </c>
-      <c r="G78" s="14" t="n"/>
-      <c r="H78" s="14" t="n"/>
-      <c r="I78" s="14" t="n"/>
-      <c r="J78" s="14" t="n"/>
-      <c r="K78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>71400041</v>
+        <v>47560024</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>0.92%→1.38%</t>
+          <t>7.93%→8.18%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>32→48</t>
+          <t>287→297</t>
         </is>
       </c>
       <c r="G79" s="14" t="n"/>
@@ -2484,23 +2525,23 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>1576401</v>
+        <v>49360025</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>7.79%→6.82%</t>
+          <t>7.16%→7.44%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>2,677→2,681</t>
+          <t>250→260</t>
         </is>
       </c>
       <c r="G80" s="14" t="n"/>
@@ -2509,142 +2550,399 @@
       <c r="J80" s="14" t="n"/>
       <c r="K80" s="14" t="n"/>
     </row>
-    <row r="82" ht="19" customHeight="1">
-      <c r="A82" s="19" t="inlineStr">
-        <is>
-          <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B82" s="20" t="n"/>
-      <c r="C82" s="20" t="n"/>
-      <c r="D82" s="20" t="n"/>
-      <c r="E82" s="20" t="n"/>
-      <c r="F82" s="20" t="n"/>
-      <c r="G82" s="20" t="n"/>
-      <c r="H82" s="20" t="n"/>
-      <c r="I82" s="20" t="n"/>
-      <c r="J82" s="20" t="n"/>
-      <c r="K82" s="20" t="n"/>
-    </row>
-    <row r="84" ht="19" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 1억(0.5%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
-      <c r="J84" s="4" t="n"/>
-      <c r="K84" s="4" t="n"/>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>46320023</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>6.99%→7.69%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>166→172</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="n"/>
+      <c r="H81" s="14" t="n"/>
+      <c r="I81" s="14" t="n"/>
+      <c r="J81" s="14" t="n"/>
+      <c r="K81" s="14" t="n"/>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>258</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>231168132</v>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→2.69%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>208→466</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>코세스  (편출)</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I86" s="16" t="n">
+        <v>-139562580</v>
+      </c>
+      <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>0.98%→0.00%</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>110→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>119392068</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>2.20%→2.95%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>232→314</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="n"/>
+      <c r="H87" s="14" t="n"/>
+      <c r="I87" s="14" t="n"/>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="14" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>71400041</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>0.92%→1.38%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>32→48</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="n"/>
+      <c r="H88" s="14" t="n"/>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="14" t="n"/>
+      <c r="K88" s="14" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>유니퀘스트</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>1576401</v>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>7.79%→6.82%</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>2,677→2,681</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="n"/>
+      <c r="H89" s="14" t="n"/>
+      <c r="I89" s="14" t="n"/>
+      <c r="J89" s="14" t="n"/>
+      <c r="K89" s="14" t="n"/>
+    </row>
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 2차전지액티브  (KB)      순자산 ≈ 2,095억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="n"/>
+      <c r="J91" s="4" t="n"/>
+      <c r="K91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="19" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
-      <c r="J87" s="4" t="n"/>
-      <c r="K87" s="4" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="18" t="inlineStr">
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="19" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
-      <c r="K90" s="4" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="18" t="inlineStr">
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="50">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A92:K92"/>
     <mergeCell ref="A30:K30"/>
+    <mergeCell ref="G77:K77"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A98:K98"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G39:K39"/>
-    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A94:K94"/>
     <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A88:K88"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A87:K87"/>
-    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="G62:K62"/>
     <mergeCell ref="A74:K74"/>
+    <mergeCell ref="G68:K68"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G15:K15"/>
+    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="A95:K95"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A85:K85"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A76:K76"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="G64:K64"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A91:K91"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A97:K97"/>
+    <mergeCell ref="A100:K100"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="G47:K47"/>
     <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="G75:K75"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="G84:K84"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="G9:K9"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 19/19  ·  전부 반영 완료</t>
+          <t>캡처 23/23  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 21억(0.5%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2046,7 +2046,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 비메모리반도체액티브  (KB)      순자산 ≈ 2,226억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 1종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2061,354 +2061,338 @@
       <c r="K61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코리아테크액티브  (미래에셋)      순자산 ≈ 2,650억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H66" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr">
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>237970700</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>0.95%→1.02%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>113→124</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>-628002100</v>
+      </c>
+      <c r="J67" s="17" t="inlineStr">
+        <is>
+          <t>1.44%→1.11%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>96→79</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>388703700</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>1.03%→1.18%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>21→24</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="n"/>
+      <c r="H68" s="14" t="n"/>
+      <c r="I68" s="14" t="n"/>
+      <c r="J68" s="14" t="n"/>
+      <c r="K68" s="14" t="n"/>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 비메모리반도체액티브  (KB)      순자산 ≈ 2,226억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>이수페타시스</t>
         </is>
       </c>
-      <c r="B64" s="11" t="n">
+      <c r="B73" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C73" s="11" t="n">
         <v>1144756800</v>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>5.50%→6.11%</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>294→321</t>
         </is>
       </c>
-      <c r="G64" s="15" t="inlineStr">
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="H64" s="16" t="n">
+      <c r="H73" s="16" t="n">
         <v>-50</v>
       </c>
-      <c r="I64" s="16" t="n">
+      <c r="I73" s="16" t="n">
         <v>-2367390000</v>
       </c>
-      <c r="J64" s="17" t="inlineStr">
+      <c r="J73" s="17" t="inlineStr">
         <is>
           <t>6.83%→5.12%</t>
         </is>
       </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="K73" s="13" t="inlineStr">
         <is>
           <t>291→241</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="B65" s="11" t="n">
+      <c r="B74" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="11" t="n">
+      <c r="C74" s="11" t="n">
         <v>317988000</v>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>19.83%→20.36%</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>425→428</t>
         </is>
       </c>
-      <c r="G65" s="14" t="n"/>
-      <c r="H65" s="14" t="n"/>
-      <c r="I65" s="14" t="n"/>
-      <c r="J65" s="14" t="n"/>
-      <c r="K65" s="14" t="n"/>
-    </row>
-    <row r="67" ht="19" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="C70" s="11" t="n">
-        <v>761484000</v>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>4.31%→5.14%</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>209→255</t>
-        </is>
-      </c>
-      <c r="G70" s="15" t="inlineStr">
-        <is>
-          <t>대한전선</t>
-        </is>
-      </c>
-      <c r="H70" s="16" t="n">
-        <v>-1215</v>
-      </c>
-      <c r="I70" s="16" t="n">
-        <v>-832396500</v>
-      </c>
-      <c r="J70" s="17" t="inlineStr">
-        <is>
-          <t>2.89%→1.78%</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C71" s="11" t="n">
-        <v>890692000</v>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>3.07%→4.19%</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H71" s="16" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I71" s="16" t="n">
-        <v>-807007500</v>
-      </c>
-      <c r="J71" s="17" t="inlineStr">
-        <is>
-          <t>1.96%→0.91%</t>
-        </is>
-      </c>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>225→108</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="G74" s="14" t="n"/>
+      <c r="H74" s="14" t="n"/>
+      <c r="I74" s="14" t="n"/>
+      <c r="J74" s="14" t="n"/>
+      <c r="K74" s="14" t="n"/>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 반도체소부장액티브  (KB)      순자산 ≈ 174억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 3종목  /  매도 0종목</t>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B76" s="4" t="n"/>
@@ -2497,332 +2481,520 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>47560024</v>
+        <v>761484000</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>7.93%→8.18%</t>
+          <t>4.31%→5.14%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>287→297</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="n"/>
-      <c r="H79" s="14" t="n"/>
-      <c r="I79" s="14" t="n"/>
-      <c r="J79" s="14" t="n"/>
-      <c r="K79" s="14" t="n"/>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H79" s="16" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I79" s="16" t="n">
+        <v>-832396500</v>
+      </c>
+      <c r="J79" s="17" t="inlineStr">
+        <is>
+          <t>2.89%→1.78%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>49360025</v>
+        <v>890692000</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>7.16%→7.44%</t>
+          <t>3.07%→4.19%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>250→260</t>
-        </is>
-      </c>
-      <c r="G80" s="14" t="n"/>
-      <c r="H80" s="14" t="n"/>
-      <c r="I80" s="14" t="n"/>
-      <c r="J80" s="14" t="n"/>
-      <c r="K80" s="14" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C81" s="11" t="n">
-        <v>46320023</v>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>6.99%→7.69%</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>166→172</t>
-        </is>
-      </c>
-      <c r="G81" s="14" t="n"/>
-      <c r="H81" s="14" t="n"/>
-      <c r="I81" s="14" t="n"/>
-      <c r="J81" s="14" t="n"/>
-      <c r="K81" s="14" t="n"/>
-    </row>
-    <row r="83" ht="19" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 1종목</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n"/>
-      <c r="K83" s="4" t="n"/>
+          <t>63→85</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>삼성에스디에스</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I80" s="16" t="n">
+        <v>-807007500</v>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>1.96%→0.91%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>225→108</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 5억(1.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 7종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="8" t="n"/>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K85" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>585779040</v>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>-541</v>
+      </c>
+      <c r="I85" s="16" t="n">
+        <v>-716500400</v>
+      </c>
+      <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>3.21%→1.15%</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
-        <v>258</v>
+        <v>324</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>231168132</v>
+        <v>577886400</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>1.12%→2.69%</t>
+          <t>0.00%→1.56%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>208→466</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>코세스  (편출)</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H86" s="16" t="n">
-        <v>-110</v>
+        <v>-513</v>
       </c>
       <c r="I86" s="16" t="n">
-        <v>-139562580</v>
+        <v>-438102000</v>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>0.98%→0.00%</t>
+          <t>1.26%→0.00%</t>
         </is>
       </c>
       <c r="K86" s="13" t="inlineStr">
         <is>
-          <t>110→0</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>119392068</v>
+        <v>766458000</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>2.20%→2.95%</t>
+          <t>0.00%→2.08%</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>232→314</t>
-        </is>
-      </c>
-      <c r="G87" s="14" t="n"/>
-      <c r="H87" s="14" t="n"/>
-      <c r="I87" s="14" t="n"/>
-      <c r="J87" s="14" t="n"/>
-      <c r="K87" s="14" t="n"/>
+          <t>0→165</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>에스티아이</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="n">
+        <v>-492</v>
+      </c>
+      <c r="I87" s="16" t="n">
+        <v>-393304800</v>
+      </c>
+      <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>2.72%→1.81%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>1,328→836</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>71400041</v>
+        <v>345982000</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>0.92%→1.38%</t>
+          <t>5.31%→6.47%</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>32→48</t>
-        </is>
-      </c>
-      <c r="G88" s="14" t="n"/>
-      <c r="H88" s="14" t="n"/>
-      <c r="I88" s="14" t="n"/>
-      <c r="J88" s="14" t="n"/>
-      <c r="K88" s="14" t="n"/>
+          <t>384→449</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>솔루엠  (편출)</t>
+        </is>
+      </c>
+      <c r="H88" s="16" t="n">
+        <v>-325</v>
+      </c>
+      <c r="I88" s="16" t="n">
+        <v>-128856000</v>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>0.37%→0.00%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>325→0</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>1576401</v>
+        <v>88242000</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>7.79%→6.82%</t>
+          <t>4.78%→4.90%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>2,677→2,681</t>
-        </is>
-      </c>
-      <c r="G89" s="14" t="n"/>
-      <c r="H89" s="14" t="n"/>
-      <c r="I89" s="14" t="n"/>
-      <c r="J89" s="14" t="n"/>
-      <c r="K89" s="14" t="n"/>
-    </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 2차전지액티브  (KB)      순자산 ≈ 2,095억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
-      <c r="H91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
+          <t>644→677</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>-212</v>
+      </c>
+      <c r="I89" s="16" t="n">
+        <v>-364470400</v>
+      </c>
+      <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>2.80%→1.75%</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>588→376</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>97272000</v>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>5.35%→5.99%</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>391→409</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>-136</v>
+      </c>
+      <c r="I90" s="16" t="n">
+        <v>-363664000</v>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>1.60%→0.58%</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>216→80</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>109704000</v>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>1.17%→1.49%</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>12→15</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
+        <is>
+          <t>HD현대일렉트릭  (편출)</t>
+        </is>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I91" s="16" t="n">
+        <v>-100800000</v>
+      </c>
+      <c r="J91" s="17" t="inlineStr">
+        <is>
+          <t>0.29%→0.00%</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>8→0</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
+      <c r="A92" s="14" t="n"/>
+      <c r="B92" s="14" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="14" t="n"/>
+      <c r="E92" s="14" t="n"/>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>두산  (편출)</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I92" s="16" t="n">
+        <v>-186592000</v>
+      </c>
+      <c r="J92" s="17" t="inlineStr">
+        <is>
+          <t>0.54%→0.00%</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>7→0</t>
         </is>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B94" s="4" t="n"/>
@@ -2846,7 +3018,7 @@
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 반도체소부장액티브  (KB)      순자산 ≈ 174억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 3종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
@@ -2861,88 +3033,560 @@
       <c r="K97" s="4" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="18" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>47560024</v>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>7.93%→8.18%</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>287→297</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="n"/>
+      <c r="H100" s="14" t="n"/>
+      <c r="I100" s="14" t="n"/>
+      <c r="J100" s="14" t="n"/>
+      <c r="K100" s="14" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>49360025</v>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>7.16%→7.44%</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>250→260</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="n"/>
+      <c r="H101" s="14" t="n"/>
+      <c r="I101" s="14" t="n"/>
+      <c r="J101" s="14" t="n"/>
+      <c r="K101" s="14" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>46320023</v>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>6.99%→7.69%</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>166→172</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="n"/>
+      <c r="H102" s="14" t="n"/>
+      <c r="I102" s="14" t="n"/>
+      <c r="J102" s="14" t="n"/>
+      <c r="K102" s="14" t="n"/>
+    </row>
+    <row r="104" ht="19" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 4종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>258</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>231168132</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→2.69%</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>208→466</t>
+        </is>
+      </c>
+      <c r="G107" s="15" t="inlineStr">
+        <is>
+          <t>코세스  (편출)</t>
+        </is>
+      </c>
+      <c r="H107" s="16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I107" s="16" t="n">
+        <v>-139562580</v>
+      </c>
+      <c r="J107" s="17" t="inlineStr">
+        <is>
+          <t>0.98%→0.00%</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>110→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>119392068</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>2.20%→2.95%</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>232→314</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="n"/>
+      <c r="H108" s="14" t="n"/>
+      <c r="I108" s="14" t="n"/>
+      <c r="J108" s="14" t="n"/>
+      <c r="K108" s="14" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>71400041</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>0.92%→1.38%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>32→48</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="n"/>
+      <c r="H109" s="14" t="n"/>
+      <c r="I109" s="14" t="n"/>
+      <c r="J109" s="14" t="n"/>
+      <c r="K109" s="14" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>유니퀘스트</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>1576401</v>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>7.79%→6.82%</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>2,677→2,681</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="n"/>
+      <c r="H110" s="14" t="n"/>
+      <c r="I110" s="14" t="n"/>
+      <c r="J110" s="14" t="n"/>
+      <c r="K110" s="14" t="n"/>
+    </row>
+    <row r="112" ht="19" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 2차전지액티브  (KB)      순자산 ≈ 2,095억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="19" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="115" ht="19" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="19" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="19" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.3%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="19" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="4" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
+      <c r="K124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="60">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A83:K83"/>
-    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="G105:K105"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="G77:K77"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A64:K64"/>
     <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="G71:K71"/>
+    <mergeCell ref="G98:K98"/>
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G39:K39"/>
+    <mergeCell ref="A70:K70"/>
     <mergeCell ref="A94:K94"/>
     <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A124:K124"/>
     <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="G62:K62"/>
-    <mergeCell ref="A74:K74"/>
-    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="A118:K118"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="G83:K83"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G15:K15"/>
-    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="A104:K104"/>
     <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A113:K113"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G65:K65"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A76:K76"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A116:K116"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A122:K122"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A97:K97"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A97:K97"/>
-    <mergeCell ref="A100:K100"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="G47:K47"/>
+    <mergeCell ref="A112:K112"/>
     <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="G84:K84"/>
+    <mergeCell ref="A125:K125"/>
+    <mergeCell ref="A121:K121"/>
+    <mergeCell ref="A115:K115"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20261029.xlsx
+++ b/reports/pdf_change_20261029.xlsx
@@ -1887,23 +1887,23 @@
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H52" s="16" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>-305645927</v>
+        <v>-97714077</v>
       </c>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t>2.76%→1.53%</t>
+          <t>1.08%→0.69%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>28→17</t>
+          <t>35→24</t>
         </is>
       </c>
     </row>
@@ -1915,23 +1915,23 @@
       <c r="E53" s="14" t="n"/>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H53" s="16" t="n">
         <v>-11</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>-97714077</v>
+        <v>-305645927</v>
       </c>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>1.08%→0.69%</t>
+          <t>2.76%→1.53%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>35→24</t>
+          <t>28→17</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 21억(0.5%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2569,7 +2569,7 @@
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 5억(1.4%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 7종목  /  매도 8종목</t>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B82" s="4" t="n"/>
@@ -3480,7 +3480,7 @@
     <row r="121" ht="19" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.3%)      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억      당일 2026-10-29  vs  전영업일 2026-10-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B121" s="4" t="n"/>
